--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdInvestDealQuery001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdInvestDealQuery001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14652" windowHeight="1932"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14650" windowHeight="1930"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>有效状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,6 +73,18 @@
   </si>
   <si>
     <t>是否转仓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利率%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银行间成交编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -426,30 +438,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="6" max="6" width="16.08984375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" customWidth="1"/>
-    <col min="12" max="12" width="35.44140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.109375" customWidth="1"/>
-    <col min="14" max="14" width="14.88671875" customWidth="1"/>
-    <col min="15" max="15" width="13.88671875" customWidth="1"/>
-    <col min="16" max="16" width="15.88671875" customWidth="1"/>
-    <col min="17" max="17" width="18.77734375" customWidth="1"/>
-    <col min="18" max="18" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" customWidth="1"/>
+    <col min="10" max="10" width="15.81640625" customWidth="1"/>
+    <col min="11" max="11" width="15.1796875" customWidth="1"/>
+    <col min="12" max="12" width="35.453125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08984375" customWidth="1"/>
+    <col min="14" max="14" width="14.90625" customWidth="1"/>
+    <col min="15" max="15" width="13.90625" customWidth="1"/>
+    <col min="16" max="16" width="15.90625" customWidth="1"/>
+    <col min="17" max="17" width="18.81640625" customWidth="1"/>
+    <col min="18" max="18" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,6 +515,15 @@
       </c>
       <c r="R1" t="s">
         <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -515,7 +536,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -525,7 +546,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
